--- a/DataTables/Datas/battle.card_effect.xlsx
+++ b/DataTables/Datas/battle.card_effect.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0056B7EA-FADE-420B-B5B6-D284EB2433D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860F3304-8E12-4997-A30F-3151E108B3FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9060" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="0" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
@@ -76,6 +76,18 @@
   </si>
   <si>
     <t>Strength</t>
+  </si>
+  <si>
+    <t>DealDamage</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>GainBlock</t>
+  </si>
+  <si>
+    <t>ApplyVulnerable</t>
   </si>
 </sst>
 </file>
@@ -439,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
@@ -519,6 +531,62 @@
         <v>3</v>
       </c>
     </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B6">
+        <v>4002</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B7">
+        <v>4003</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B8">
+        <v>4004</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B9">
+        <v>4005</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DataTables/Datas/battle.card_effect.xlsx
+++ b/DataTables/Datas/battle.card_effect.xlsx
@@ -94,7 +94,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,13 +110,123 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF365F91"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F7FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F8FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F9F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF9EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F4FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF5F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F8F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F0F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F2E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7EFCF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFE7F5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5E9E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F1F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -133,8 +243,50 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFill="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -462,128 +614,128 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="1">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="1">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="1">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="2">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="2">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="2">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="3">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="4">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="4">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="4">
         <v>12</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="4">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" t="s" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B5">
+      <c r="B5" s="7">
         <v>4001</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="8">
         <v>15</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" t="s" s="9">
         <v>16</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B6">
+      <c r="B6" s="11">
         <v>4002</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" t="s" s="12">
         <v>17</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" t="s" s="13">
         <v>18</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="14">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B7">
+      <c r="B7" s="7">
         <v>4003</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" t="s" s="8">
         <v>19</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" t="s" s="9">
         <v>18</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B8">
+      <c r="B8" s="11">
         <v>4004</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" t="s" s="12">
         <v>17</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" t="s" s="13">
         <v>18</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="14">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B9">
+      <c r="B9" s="7">
         <v>4005</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" t="s" s="8">
         <v>20</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" t="s" s="9">
         <v>18</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="10">
         <v>2</v>
       </c>
     </row>

--- a/DataTables/Datas/battle.card_effect.xlsx
+++ b/DataTables/Datas/battle.card_effect.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Redf4e79157914bb9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3c3d74be5c084791"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -195,7 +195,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="15">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -240,6 +240,15 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -445,7 +454,7 @@
   <x:cols>
     <x:col min="1" max="1" width="8.75" customWidth="1"/>
     <x:col min="2" max="2" width="9.5" customWidth="1"/>
-    <x:col min="3" max="3" width="15.625" customWidth="1"/>
+    <x:col min="3" max="3" width="24.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="14.25" customWidth="1"/>
     <x:col min="5" max="5" width="6" customWidth="1"/>
   </x:cols>
@@ -591,6 +600,201 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
+    <x:row r="11">
+      <x:c r="A11"/>
+      <x:c r="B11" t="n">
+        <x:v>4007</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>DealDamage</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="E11" t="n">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12"/>
+      <x:c r="B12" t="n">
+        <x:v>4008</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>DealDamage</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="E12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13"/>
+      <x:c r="B13" t="n">
+        <x:v>4009</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>DealDamage</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="E13" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14" t="n">
+        <x:v>4010</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>DrawCards</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="E14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15"/>
+      <x:c r="B15" t="n">
+        <x:v>4011</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>GainBlock</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="E15" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16"/>
+      <x:c r="B16" t="n">
+        <x:v>4012</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>ExhaustSelectedHandCard</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="E16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17"/>
+      <x:c r="B17" t="n">
+        <x:v>4013</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>DrawCards</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="E17" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18"/>
+      <x:c r="B18" s="17" t="n">
+        <x:v>4014</x:v>
+      </x:c>
+      <x:c r="C18" s="17" t="str">
+        <x:v>Heal</x:v>
+      </x:c>
+      <x:c r="D18" s="17" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="E18" s="17" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19"/>
+      <x:c r="B19" t="n">
+        <x:v>4015</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>DealDamage</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="E19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20"/>
+      <x:c r="B20" t="n">
+        <x:v>4016</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>DealDamageFromSourceBlock</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="E20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21"/>
+      <x:c r="B21" t="n">
+        <x:v>4017</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>RetainBlock</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="E21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22"/>
+      <x:c r="B22" t="n">
+        <x:v>4018</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>PlayTopDrawCardAndExhaust</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="E22" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23"/>
+      <x:c r="B23" t="n">
+        <x:v>4019</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>RegisterBlockGainRandomEnemyDamage</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="E23" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
